--- a/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
+++ b/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-26T12:33:39+00:00</t>
+    <t>2024-09-26T13:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
+++ b/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-26T13:53:54+00:00</t>
+    <t>2024-09-27T09:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
+++ b/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T09:10:18+00:00</t>
+    <t>2024-09-27T09:21:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
+++ b/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T09:21:46+00:00</t>
+    <t>2024-10-01T12:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
+++ b/149-partie-fonctionnelle-description-des-éléments-mos-profilés/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-01T12:01:38+00:00</t>
+    <t>2024-10-02T08:53:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
